--- a/data/output/inconsistencias.xlsx
+++ b/data/output/inconsistencias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,22 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>errors</t>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>message</t>
         </is>
       </c>
     </row>
@@ -446,7 +461,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Notebook: CFOP não informado.</t>
+          <t>CFOP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CFOP</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Notebook</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CFOP não informado.</t>
         </is>
       </c>
     </row>
@@ -463,7 +493,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Notebook: CFOP 9999 inválido.</t>
+          <t>CFOP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CFOP</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Notebook</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CFOP 9999 inválido.</t>
         </is>
       </c>
     </row>
@@ -475,10 +520,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CNPJ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CNPJ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Emitente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CNPJ 1111111111111 inválido.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -493,7 +557,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Notebook: NCM não informado.</t>
+          <t>NCM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NCM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notebook</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NCM não informado.</t>
         </is>
       </c>
     </row>
@@ -510,7 +589,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Notebook: NCM 99999999 inválido.</t>
+          <t>NCM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NCM</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Notebook</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NCM 99999999 inválido.</t>
         </is>
       </c>
     </row>
@@ -526,6 +620,9 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -540,7 +637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Divergência de total: diferença 1000.00</t>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>vNF</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Nota Fiscal</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diferença de total: 1000.00</t>
         </is>
       </c>
     </row>
